--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2401-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2401-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F06429E3-4FE7-4B87-91A1-8435716A00C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1443DA6A-6CBA-4530-89E1-8916350BF942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{7EDDDD80-EAA5-41C7-9C49-E66F2E033710}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{C4B0093F-4416-4AA5-8CDA-DF2CE0E7738B}"/>
   </bookViews>
   <sheets>
     <sheet name="2401-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1469,25 +1469,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9F27E90-5B39-48CD-99D1-CDFD82A1BE3C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF7452D9-0A28-4B66-9AD2-193DB27DD24D}">
   <dimension ref="A1:X38"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1521,7 +1520,7 @@
       <c r="W1" s="27"/>
       <c r="X1" s="19"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -1557,7 +1556,7 @@
       <c r="W2" s="29"/>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
@@ -1609,7 +1608,7 @@
       </c>
       <c r="X3" s="33"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
       <c r="C4" s="7"/>
@@ -1677,7 +1676,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <v>2024</v>
       </c>
@@ -1749,7 +1748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="36">
         <v>2023</v>
       </c>
@@ -1821,7 +1820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="34">
         <v>2022</v>
       </c>
@@ -1893,7 +1892,7 @@
         <v>2.71</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="36">
         <v>2021</v>
       </c>
@@ -1965,7 +1964,7 @@
         <v>9.8800000000000008</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="34">
         <v>2020</v>
       </c>
@@ -2037,7 +2036,7 @@
         <v>3.06</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <v>2019</v>
       </c>
@@ -2109,7 +2108,7 @@
         <v>4.04</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="34">
         <v>2018</v>
       </c>
@@ -2181,7 +2180,7 @@
         <v>3.32</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>2017</v>
       </c>
@@ -2253,7 +2252,7 @@
         <v>7.25</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="34">
         <v>2016</v>
       </c>
@@ -2325,7 +2324,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <v>2015</v>
       </c>
@@ -2397,7 +2396,7 @@
         <v>9.02</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="34">
         <v>2014</v>
       </c>
@@ -2469,7 +2468,7 @@
         <v>6.24</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2013</v>
       </c>
@@ -2541,7 +2540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="34">
         <v>2012</v>
       </c>
@@ -2613,7 +2612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>2011</v>
       </c>
@@ -2685,7 +2684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="34">
         <v>2010</v>
       </c>
@@ -2757,7 +2756,7 @@
         <v>9.16</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="36">
         <v>2009</v>
       </c>
@@ -2829,7 +2828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="34">
         <v>2008</v>
       </c>
@@ -2901,7 +2900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="36">
         <v>2007</v>
       </c>
@@ -2973,7 +2972,7 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="34">
         <v>2006</v>
       </c>
@@ -3045,7 +3044,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="36">
         <v>2005</v>
       </c>
@@ -3117,7 +3116,7 @@
         <v>8.76</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="34">
         <v>2004</v>
       </c>
@@ -3189,7 +3188,7 @@
         <v>9.51</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="36">
         <v>2003</v>
       </c>
@@ -3261,7 +3260,7 @@
         <v>6.23</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="34">
         <v>2002</v>
       </c>
@@ -3333,7 +3332,7 @@
         <v>8.67</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>2001</v>
       </c>
@@ -3405,7 +3404,7 @@
         <v>7.48</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="34">
         <v>2000</v>
       </c>
@@ -3477,7 +3476,7 @@
         <v>7.76</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="36">
         <v>1999</v>
       </c>
@@ -3549,7 +3548,7 @@
         <v>3.51</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="34">
         <v>1998</v>
       </c>
@@ -3621,7 +3620,7 @@
         <v>4.91</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="36">
         <v>1997</v>
       </c>
@@ -3693,7 +3692,7 @@
         <v>9.09</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="34">
         <v>1996</v>
       </c>
@@ -3765,7 +3764,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="36">
         <v>1995</v>
       </c>
@@ -3837,7 +3836,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="34">
         <v>1994</v>
       </c>
@@ -3909,7 +3908,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="36">
         <v>1993</v>
       </c>
@@ -3981,7 +3980,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="34">
         <v>1992</v>
       </c>
@@ -4053,7 +4052,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="36" t="s">
         <v>48</v>
       </c>
